--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251001_164854.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251001_164854.xlsx
@@ -5066,7 +5066,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251001_164854.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251001_164854.xlsx
@@ -5066,7 +5066,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
